--- a/output_boron/boron_Intermediate_pearson_2000.xlsx
+++ b/output_boron/boron_Intermediate_pearson_2000.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
   <si>
     <t>NA</t>
   </si>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">10.1038/35021000</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/boron_isotopes_pearson_2000.xlsx</t>
+    <t xml:space="preserve">boron_isotopes_pearson_2000_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1458,6 +1458,66 @@
   </si>
   <si>
     <t xml:space="preserve">872_C_13_5_20_22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">872_C_14_4_20_22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">865_C_5_1_110_112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. topilensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">865_C_6_2_65_67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">865_C_7_1_110_112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">865_C_7_3_110_112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. praetopilensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">865_C_8_3_110_112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">865_C_8_5_110_112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">865_C_9_5_110_112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">865_C_10_1_110_112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M. caucasica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">865_C_10_5_100_102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">425-500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">865_C_11_1_110_112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M. marginodentata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">865_C_12_5_110_112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M. velascoensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">865_C_14_3_110_112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">865_C_15_5_110_112</t>
   </si>
 </sst>
 </file>
@@ -1465,7 +1525,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1525,12 +1585,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1644,7 +1698,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1726,7 +1780,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2333,7 +2386,7 @@
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" t="s">
         <v>242</v>
       </c>
       <c r="D5" t="s">
@@ -2410,7 +2463,7 @@
       <c r="B6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
       <c r="D6" t="s">
@@ -2487,7 +2540,7 @@
       <c r="B7" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" t="s">
         <v>242</v>
       </c>
       <c r="D7" t="s">
@@ -2564,7 +2617,7 @@
       <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
       <c r="D8" t="s">
@@ -2641,7 +2694,7 @@
       <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
@@ -2718,7 +2771,7 @@
       <c r="B10" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" t="s">
         <v>242</v>
       </c>
       <c r="D10" t="s">
@@ -2795,7 +2848,7 @@
       <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" t="s">
         <v>242</v>
       </c>
       <c r="D11" t="s">
@@ -2872,7 +2925,7 @@
       <c r="B12" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" t="s">
         <v>242</v>
       </c>
       <c r="D12" t="s">
@@ -2949,7 +3002,7 @@
       <c r="B13" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" t="s">
         <v>242</v>
       </c>
       <c r="D13" t="s">
@@ -3026,7 +3079,7 @@
       <c r="B14" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" t="s">
         <v>242</v>
       </c>
       <c r="D14" t="s">
@@ -3103,7 +3156,7 @@
       <c r="B15" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" t="s">
         <v>242</v>
       </c>
       <c r="D15" t="s">
@@ -3180,7 +3233,7 @@
       <c r="B16" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" t="s">
         <v>242</v>
       </c>
       <c r="D16" t="s">
@@ -3257,7 +3310,7 @@
       <c r="B17" t="s">
         <v>241</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" t="s">
         <v>242</v>
       </c>
       <c r="D17" t="s">
@@ -3334,7 +3387,7 @@
       <c r="B18" t="s">
         <v>241</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" t="s">
         <v>242</v>
       </c>
       <c r="D18" t="s">
@@ -3411,7 +3464,7 @@
       <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" t="s">
         <v>242</v>
       </c>
       <c r="D19" t="s">
@@ -3488,7 +3541,7 @@
       <c r="B20" t="s">
         <v>241</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" t="s">
         <v>242</v>
       </c>
       <c r="D20" t="s">
@@ -3565,7 +3618,7 @@
       <c r="B21" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" t="s">
         <v>242</v>
       </c>
       <c r="D21" t="s">
@@ -3642,7 +3695,7 @@
       <c r="B22" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" t="s">
         <v>242</v>
       </c>
       <c r="D22" t="s">
@@ -3719,7 +3772,7 @@
       <c r="B23" t="s">
         <v>241</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" t="s">
         <v>242</v>
       </c>
       <c r="D23" t="s">
@@ -3796,7 +3849,7 @@
       <c r="B24" t="s">
         <v>241</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" t="s">
         <v>242</v>
       </c>
       <c r="D24" t="s">
@@ -3873,7 +3926,7 @@
       <c r="B25" t="s">
         <v>241</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" t="s">
         <v>242</v>
       </c>
       <c r="D25" t="s">
@@ -3944,46 +3997,1082 @@
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
-      <c r="U26" s="9"/>
+      <c r="A26" t="s">
+        <v>272</v>
+      </c>
+      <c r="B26" t="s">
+        <v>241</v>
+      </c>
+      <c r="C26" t="s">
+        <v>242</v>
+      </c>
+      <c r="D26" t="s">
+        <v>243</v>
+      </c>
+      <c r="E26" t="s">
+        <v>244</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10.10055556</v>
+      </c>
+      <c r="G26" t="n">
+        <v>162.86722222</v>
+      </c>
+      <c r="H26" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="I26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J26" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="L26" t="s">
+        <v>245</v>
+      </c>
+      <c r="M26" t="s">
+        <v>250</v>
+      </c>
+      <c r="N26" t="s">
+        <v>263</v>
+      </c>
+      <c r="O26" t="s">
+        <v>247</v>
+      </c>
+      <c r="P26" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U26" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="V26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y26" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="27" ht="19" customHeight="1">
-      <c r="U27" s="9"/>
+      <c r="A27" t="s">
+        <v>273</v>
+      </c>
+      <c r="B27" t="s">
+        <v>241</v>
+      </c>
+      <c r="C27" t="s">
+        <v>242</v>
+      </c>
+      <c r="D27" t="s">
+        <v>243</v>
+      </c>
+      <c r="E27" t="s">
+        <v>244</v>
+      </c>
+      <c r="F27" t="n">
+        <v>18.55138889</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-179.64416667</v>
+      </c>
+      <c r="H27" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="I27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J27" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="L27" t="s">
+        <v>245</v>
+      </c>
+      <c r="M27" t="s">
+        <v>274</v>
+      </c>
+      <c r="N27" t="s">
+        <v>263</v>
+      </c>
+      <c r="O27" t="s">
+        <v>247</v>
+      </c>
+      <c r="P27" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>23</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U27" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="V27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y27" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="28" ht="19" customHeight="1">
-      <c r="U28" s="9"/>
+      <c r="A28" t="s">
+        <v>275</v>
+      </c>
+      <c r="B28" t="s">
+        <v>241</v>
+      </c>
+      <c r="C28" t="s">
+        <v>242</v>
+      </c>
+      <c r="D28" t="s">
+        <v>243</v>
+      </c>
+      <c r="E28" t="s">
+        <v>244</v>
+      </c>
+      <c r="F28" t="n">
+        <v>18.55138889</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-179.64416667</v>
+      </c>
+      <c r="H28" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="I28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J28" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="L28" t="s">
+        <v>245</v>
+      </c>
+      <c r="M28" t="s">
+        <v>246</v>
+      </c>
+      <c r="N28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="O28" t="s">
+        <v>247</v>
+      </c>
+      <c r="P28" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>25</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U28" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="V28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y28" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="29" ht="19" customHeight="1">
-      <c r="U29" s="9"/>
+      <c r="A29" t="s">
+        <v>276</v>
+      </c>
+      <c r="B29" t="s">
+        <v>241</v>
+      </c>
+      <c r="C29" t="s">
+        <v>242</v>
+      </c>
+      <c r="D29" t="s">
+        <v>243</v>
+      </c>
+      <c r="E29" t="s">
+        <v>244</v>
+      </c>
+      <c r="F29" t="n">
+        <v>18.55138889</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-179.64416667</v>
+      </c>
+      <c r="H29" t="n">
+        <v>44.26</v>
+      </c>
+      <c r="I29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J29" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="L29" t="s">
+        <v>245</v>
+      </c>
+      <c r="M29" t="s">
+        <v>274</v>
+      </c>
+      <c r="N29" t="s">
+        <v>263</v>
+      </c>
+      <c r="O29" t="s">
+        <v>247</v>
+      </c>
+      <c r="P29" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U29" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="V29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y29" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="30" ht="19" customHeight="1">
-      <c r="U30" s="9"/>
+      <c r="A30" t="s">
+        <v>277</v>
+      </c>
+      <c r="B30" t="s">
+        <v>241</v>
+      </c>
+      <c r="C30" t="s">
+        <v>242</v>
+      </c>
+      <c r="D30" t="s">
+        <v>243</v>
+      </c>
+      <c r="E30" t="s">
+        <v>244</v>
+      </c>
+      <c r="F30" t="n">
+        <v>18.55138889</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-179.64416667</v>
+      </c>
+      <c r="H30" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="I30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J30" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="L30" t="s">
+        <v>245</v>
+      </c>
+      <c r="M30" t="s">
+        <v>278</v>
+      </c>
+      <c r="N30" t="s">
+        <v>263</v>
+      </c>
+      <c r="O30" t="s">
+        <v>247</v>
+      </c>
+      <c r="P30" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U30" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="V30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y30" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="31" ht="19" customHeight="1">
-      <c r="U31" s="9"/>
+      <c r="A31" t="s">
+        <v>279</v>
+      </c>
+      <c r="B31" t="s">
+        <v>241</v>
+      </c>
+      <c r="C31" t="s">
+        <v>242</v>
+      </c>
+      <c r="D31" t="s">
+        <v>243</v>
+      </c>
+      <c r="E31" t="s">
+        <v>244</v>
+      </c>
+      <c r="F31" t="n">
+        <v>18.55138889</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-179.64416667</v>
+      </c>
+      <c r="H31" t="n">
+        <v>46.07</v>
+      </c>
+      <c r="I31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J31" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="K31" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="L31" t="s">
+        <v>245</v>
+      </c>
+      <c r="M31" t="s">
+        <v>278</v>
+      </c>
+      <c r="N31" t="s">
+        <v>263</v>
+      </c>
+      <c r="O31" t="s">
+        <v>247</v>
+      </c>
+      <c r="P31" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>22</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U31" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="V31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y31" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="32" ht="19" customHeight="1">
-      <c r="U32" s="9"/>
+      <c r="A32" t="s">
+        <v>280</v>
+      </c>
+      <c r="B32" t="s">
+        <v>241</v>
+      </c>
+      <c r="C32" t="s">
+        <v>242</v>
+      </c>
+      <c r="D32" t="s">
+        <v>243</v>
+      </c>
+      <c r="E32" t="s">
+        <v>244</v>
+      </c>
+      <c r="F32" t="n">
+        <v>18.55138889</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-179.64416667</v>
+      </c>
+      <c r="H32" t="n">
+        <v>46.97</v>
+      </c>
+      <c r="I32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J32" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>49</v>
+      </c>
+      <c r="L32" t="s">
+        <v>245</v>
+      </c>
+      <c r="M32" t="s">
+        <v>278</v>
+      </c>
+      <c r="N32" t="s">
+        <v>263</v>
+      </c>
+      <c r="O32" t="s">
+        <v>247</v>
+      </c>
+      <c r="P32" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U32" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="V32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y32" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="33" ht="19" customHeight="1">
-      <c r="U33" s="9"/>
+      <c r="A33" t="s">
+        <v>281</v>
+      </c>
+      <c r="B33" t="s">
+        <v>241</v>
+      </c>
+      <c r="C33" t="s">
+        <v>242</v>
+      </c>
+      <c r="D33" t="s">
+        <v>243</v>
+      </c>
+      <c r="E33" t="s">
+        <v>244</v>
+      </c>
+      <c r="F33" t="n">
+        <v>18.55138889</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-179.64416667</v>
+      </c>
+      <c r="H33" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="I33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J33" t="n">
+        <v>49</v>
+      </c>
+      <c r="K33" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="L33" t="s">
+        <v>245</v>
+      </c>
+      <c r="M33" t="s">
+        <v>278</v>
+      </c>
+      <c r="N33" t="s">
+        <v>251</v>
+      </c>
+      <c r="O33" t="s">
+        <v>247</v>
+      </c>
+      <c r="P33" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U33" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="V33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y33" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="34" ht="19" customHeight="1">
-      <c r="U34" s="9"/>
+      <c r="A34" t="s">
+        <v>282</v>
+      </c>
+      <c r="B34" t="s">
+        <v>241</v>
+      </c>
+      <c r="C34" t="s">
+        <v>242</v>
+      </c>
+      <c r="D34" t="s">
+        <v>243</v>
+      </c>
+      <c r="E34" t="s">
+        <v>244</v>
+      </c>
+      <c r="F34" t="n">
+        <v>18.55138889</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-179.64416667</v>
+      </c>
+      <c r="H34" t="n">
+        <v>51.02</v>
+      </c>
+      <c r="I34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J34" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="K34" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="L34" t="s">
+        <v>245</v>
+      </c>
+      <c r="M34" t="s">
+        <v>283</v>
+      </c>
+      <c r="N34" t="s">
+        <v>251</v>
+      </c>
+      <c r="O34" t="s">
+        <v>247</v>
+      </c>
+      <c r="P34" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U34" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="V34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y34" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="35" ht="19" customHeight="1">
-      <c r="U35" s="9"/>
+      <c r="A35" t="s">
+        <v>284</v>
+      </c>
+      <c r="B35" t="s">
+        <v>241</v>
+      </c>
+      <c r="C35" t="s">
+        <v>242</v>
+      </c>
+      <c r="D35" t="s">
+        <v>243</v>
+      </c>
+      <c r="E35" t="s">
+        <v>244</v>
+      </c>
+      <c r="F35" t="n">
+        <v>18.55138889</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-179.64416667</v>
+      </c>
+      <c r="H35" t="n">
+        <v>52.22</v>
+      </c>
+      <c r="I35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J35" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="K35" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="L35" t="s">
+        <v>245</v>
+      </c>
+      <c r="M35" t="s">
+        <v>283</v>
+      </c>
+      <c r="N35" t="s">
+        <v>285</v>
+      </c>
+      <c r="O35" t="s">
+        <v>247</v>
+      </c>
+      <c r="P35" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U35" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="V35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X35" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y35" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="36" ht="19" customHeight="1">
-      <c r="U36" s="9"/>
+      <c r="A36" t="s">
+        <v>286</v>
+      </c>
+      <c r="B36" t="s">
+        <v>241</v>
+      </c>
+      <c r="C36" t="s">
+        <v>242</v>
+      </c>
+      <c r="D36" t="s">
+        <v>243</v>
+      </c>
+      <c r="E36" t="s">
+        <v>244</v>
+      </c>
+      <c r="F36" t="n">
+        <v>18.55138889</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-179.64416667</v>
+      </c>
+      <c r="H36" t="n">
+        <v>53.24</v>
+      </c>
+      <c r="I36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J36" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="K36" t="n">
+        <v>54</v>
+      </c>
+      <c r="L36" t="s">
+        <v>245</v>
+      </c>
+      <c r="M36" t="s">
+        <v>287</v>
+      </c>
+      <c r="N36" t="s">
+        <v>285</v>
+      </c>
+      <c r="O36" t="s">
+        <v>247</v>
+      </c>
+      <c r="P36" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U36" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="V36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X36" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y36" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="37" ht="19" customHeight="1">
-      <c r="U37" s="9"/>
+      <c r="A37" t="s">
+        <v>288</v>
+      </c>
+      <c r="B37" t="s">
+        <v>241</v>
+      </c>
+      <c r="C37" t="s">
+        <v>242</v>
+      </c>
+      <c r="D37" t="s">
+        <v>243</v>
+      </c>
+      <c r="E37" t="s">
+        <v>244</v>
+      </c>
+      <c r="F37" t="n">
+        <v>18.55138889</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-179.64416667</v>
+      </c>
+      <c r="H37" t="n">
+        <v>55.84</v>
+      </c>
+      <c r="I37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J37" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="K37" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="L37" t="s">
+        <v>245</v>
+      </c>
+      <c r="M37" t="s">
+        <v>289</v>
+      </c>
+      <c r="N37" t="s">
+        <v>285</v>
+      </c>
+      <c r="O37" t="s">
+        <v>247</v>
+      </c>
+      <c r="P37" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U37" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="V37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y37" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="38" ht="19" customHeight="1">
-      <c r="U38" s="9"/>
+      <c r="A38" t="s">
+        <v>290</v>
+      </c>
+      <c r="B38" t="s">
+        <v>241</v>
+      </c>
+      <c r="C38" t="s">
+        <v>242</v>
+      </c>
+      <c r="D38" t="s">
+        <v>243</v>
+      </c>
+      <c r="E38" t="s">
+        <v>244</v>
+      </c>
+      <c r="F38" t="n">
+        <v>18.55138889</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-179.64416667</v>
+      </c>
+      <c r="H38" t="n">
+        <v>57.12</v>
+      </c>
+      <c r="I38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J38" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="L38" t="s">
+        <v>245</v>
+      </c>
+      <c r="M38" t="s">
+        <v>289</v>
+      </c>
+      <c r="N38" t="s">
+        <v>263</v>
+      </c>
+      <c r="O38" t="s">
+        <v>247</v>
+      </c>
+      <c r="P38" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>22</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U38" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="V38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y38" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="39" ht="19" customHeight="1">
-      <c r="U39" s="9"/>
+      <c r="A39" t="s">
+        <v>291</v>
+      </c>
+      <c r="B39" t="s">
+        <v>241</v>
+      </c>
+      <c r="C39" t="s">
+        <v>242</v>
+      </c>
+      <c r="D39" t="s">
+        <v>243</v>
+      </c>
+      <c r="E39" t="s">
+        <v>244</v>
+      </c>
+      <c r="F39" t="n">
+        <v>18.55138889</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-179.64416667</v>
+      </c>
+      <c r="H39" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="I39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J39" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="K39" t="n">
+        <v>60</v>
+      </c>
+      <c r="L39" t="s">
+        <v>245</v>
+      </c>
+      <c r="M39" t="s">
+        <v>289</v>
+      </c>
+      <c r="N39" t="s">
+        <v>263</v>
+      </c>
+      <c r="O39" t="s">
+        <v>247</v>
+      </c>
+      <c r="P39" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U39" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="V39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y39" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="U40" s="9"/>
@@ -4192,29 +5281,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
